--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.38196886236001</v>
+        <v>4.774569940133501</v>
       </c>
       <c r="D2" t="n">
-        <v>26.46771283343728</v>
+        <v>4.301003335433557</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F2" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.59515270872753</v>
+        <v>6.434212315168223</v>
       </c>
       <c r="D3" t="n">
-        <v>18.85566232488734</v>
+        <v>3.064045127794192</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F3" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.81464668577772</v>
+        <v>5.169880086438879</v>
       </c>
       <c r="D4" t="n">
-        <v>9.999323715442721</v>
+        <v>1.624890103759442</v>
       </c>
       <c r="E4" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F4" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.73848877035266</v>
+        <v>3.532504425182308</v>
       </c>
       <c r="D5" t="n">
-        <v>18.96249869112721</v>
+        <v>3.081406037308172</v>
       </c>
       <c r="E5" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F5" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.33947100340166</v>
+        <v>6.555164038052769</v>
       </c>
       <c r="D6" t="n">
-        <v>10.88133041952159</v>
+        <v>1.768216193172258</v>
       </c>
       <c r="E6" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F6" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.78560249969805</v>
+        <v>1.915160406200932</v>
       </c>
       <c r="D7" t="n">
-        <v>14.3120453639335</v>
+        <v>2.325707371639194</v>
       </c>
       <c r="E7" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F7" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.52269611005097</v>
+        <v>7.397438117883283</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62906934572582</v>
+        <v>4.489723768680447</v>
       </c>
       <c r="E8" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F8" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.27281815589672</v>
+        <v>7.356832950333217</v>
       </c>
       <c r="D9" t="n">
-        <v>23.10454540486508</v>
+        <v>3.754488628290575</v>
       </c>
       <c r="E9" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F9" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.538795114541685</v>
+        <v>1.387554206113024</v>
       </c>
       <c r="D10" t="n">
-        <v>5.780570055995708</v>
+        <v>0.9393426340993025</v>
       </c>
       <c r="E10" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F10" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.5616648193153</v>
+        <v>2.853770533138736</v>
       </c>
       <c r="D11" t="n">
-        <v>1.273567944258168</v>
+        <v>0.2069547909419523</v>
       </c>
       <c r="E11" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F11" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.56764587434577</v>
+        <v>4.642242454581188</v>
       </c>
       <c r="D12" t="n">
-        <v>28.45239004138518</v>
+        <v>4.623513381725092</v>
       </c>
       <c r="E12" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F12" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.30522965636084</v>
+        <v>3.137099819158637</v>
       </c>
       <c r="D13" t="n">
-        <v>19.69825280837276</v>
+        <v>3.200966081360574</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F13" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.75555311415101</v>
+        <v>6.13527738104954</v>
       </c>
       <c r="D14" t="n">
-        <v>29.01464658489096</v>
+        <v>4.714880070044781</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F14" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.22219045664204</v>
+        <v>5.073605949204332</v>
       </c>
       <c r="D15" t="n">
-        <v>14.99980658311514</v>
+        <v>2.437468569756211</v>
       </c>
       <c r="E15" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F15" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>13.50614723416809</v>
+        <v>2.194748925552314</v>
       </c>
       <c r="D16" t="n">
-        <v>13.83613348289008</v>
+        <v>2.248371690969638</v>
       </c>
       <c r="E16" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F16" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.22171286843888</v>
+        <v>4.423528341121318</v>
       </c>
       <c r="D17" t="n">
-        <v>2.101770270891878</v>
+        <v>0.3415376690199302</v>
       </c>
       <c r="E17" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F17" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>19.76161240932794</v>
+        <v>3.21126201651579</v>
       </c>
       <c r="D18" t="n">
-        <v>19.25248316700295</v>
+        <v>3.12852851463798</v>
       </c>
       <c r="E18" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F18" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>29.36962026084997</v>
+        <v>4.772563292388121</v>
       </c>
       <c r="D19" t="n">
-        <v>28.88034402380445</v>
+        <v>4.693055903868223</v>
       </c>
       <c r="E19" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F19" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>31.44045284329523</v>
+        <v>5.109073587035476</v>
       </c>
       <c r="D20" t="n">
-        <v>31.03796800621232</v>
+        <v>5.043669801009503</v>
       </c>
       <c r="E20" t="n">
-        <v>10.6914495359704</v>
+        <v>1.737360549595189</v>
       </c>
       <c r="F20" t="n">
-        <v>9.036949298151479</v>
+        <v>1.468504260949615</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
